--- a/documents/Old English notes.xlsx
+++ b/documents/Old English notes.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -142,6 +142,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -242,28 +243,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -279,165 +284,271 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="34.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -461,7 +572,7 @@
     <hyperlink ref="F2" r:id="rId5" display="Possessive"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.845138888888889" header="0.511811023622047" footer="0.511805555555556"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.70625" header="0.511811023622047" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="true" differentOddEven="true">
     <oddHeader/>

--- a/documents/Old English notes.xlsx
+++ b/documents/Old English notes.xlsx
@@ -572,7 +572,7 @@
     <hyperlink ref="F2" r:id="rId5" display="Possessive"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.70625" header="0.511811023622047" footer="0.511805555555556"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.567361111111111" header="0.511811023622047" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="true" differentOddEven="true">
     <oddHeader/>
